--- a/downloads/korrigierte_referenz/Schule_2NF.xlsx
+++ b/downloads/korrigierte_referenz/Schule_2NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="R45af2d89f3724465"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R35a7728477e94769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="R6face521ebf843d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="Rd7f758984c8943c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R5ea7479dc78846d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="R39857364ea414cc7"/>
   </x:sheets>
 </x:workbook>
 </file>
